--- a/Docs/QA/1_Main_Screen_CL.xlsx
+++ b/Docs/QA/1_Main_Screen_CL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parkmain\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parkmain\Desktop\game\gameQALearning\Docs\QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6D8290-9D34-41B9-8414-1B3B41384B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1FB6F0-C105-454D-8603-58071EC4A18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="555" windowWidth="21015" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5580" yWindow="900" windowWidth="21015" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>Checklist ID</t>
   </si>
@@ -214,6 +214,14 @@
   </si>
   <si>
     <t>친구 버튼이 표시되고 클릭 시 친구 화면으로 이동한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>팝업창이 여러 개 켜져서 창이 popup창이 중첩되는 문제 있음</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -611,6 +619,9 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -625,6 +636,9 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -639,6 +653,9 @@
       <c r="D4" t="s">
         <v>14</v>
       </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -653,6 +670,12 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -667,6 +690,9 @@
       <c r="D6" t="s">
         <v>20</v>
       </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -681,6 +707,9 @@
       <c r="D7" t="s">
         <v>24</v>
       </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -695,6 +724,9 @@
       <c r="D8" t="s">
         <v>27</v>
       </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -709,6 +741,9 @@
       <c r="D9" t="s">
         <v>31</v>
       </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -723,6 +758,9 @@
       <c r="D10" t="s">
         <v>34</v>
       </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -737,6 +775,9 @@
       <c r="D11" t="s">
         <v>37</v>
       </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -751,6 +792,9 @@
       <c r="D12" t="s">
         <v>39</v>
       </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -765,6 +809,9 @@
       <c r="D13" t="s">
         <v>42</v>
       </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -779,6 +826,9 @@
       <c r="D14" t="s">
         <v>44</v>
       </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -793,6 +843,9 @@
       <c r="D15" t="s">
         <v>47</v>
       </c>
+      <c r="E15" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -807,8 +860,11 @@
       <c r="D16" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -821,8 +877,11 @@
       <c r="D17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -834,6 +893,9 @@
       </c>
       <c r="D18" t="s">
         <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
